--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/WASHINGTON_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/WASHINGTON_2020.xlsx
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C79">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C107">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C120">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C128">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C196">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C435">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C461">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C483">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C556">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C589">
